--- a/reports/training_logs.xlsx
+++ b/reports/training_logs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,6 +886,43 @@
         <v>6</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DiffuVQA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>checkpoints/btch4/lr0.0001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-11-30 17:26:36</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>750.3464455604553</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7503464455604554</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GPUs: 1, CUDA Version: 12.1, PyTorch Version: 2.5.1+cu121</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
